--- a/RawData/animdatadyn_master_Pdigest.xlsx
+++ b/RawData/animdatadyn_master_Pdigest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malgren/Documents/Mines/N_P/NANI_NAPI/CSNAPNIv1/RawData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/lds5498_psu_edu/Documents/CSNAPNI/CSNAPNI/CBW-CSNAPNI/CB_CSNAPNI/RawData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B43C87A6-C6D3-6744-9948-C69E7D6E5C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{B43C87A6-C6D3-6744-9948-C69E7D6E5C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA692F01-E080-094E-B4B4-F843CA42139C}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="500" windowWidth="33600" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -802,9 +824,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -842,7 +864,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -948,7 +970,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1090,7 +1112,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2937,6 +2959,10 @@
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B27" s="9"/>
+      <c r="C27" t="str" cm="1">
+        <f t="array" ref="C27">"c(" &amp; _xlfn.TEXTJOIN(",", TRUE, """" &amp; C2:Y2 &amp; """") &amp; ")"</f>
+        <v>c("Cycles per Year","Cycles per year^-1","(cycles -1)/cycles","(cycles per year^-1) * ((cycles-1)/cycles)","Days on the Farm","days on farm/365","(days on farm/365) * 0.5","Animal N Intake (kg-N/animal/yr)","Animal P Intake (kg-P/animal/yr)","N in Animal Excretion (kg-N/animal/yr)","P in Animal Excretion (kg-P/animal/yr)","Ammonia Emission (kg-N/animal/yr)","% Loss in Human Consumption","Product Weight (kg/animal)","Edible Proportion","N in Edible Proportion","kcal/kg edible ","g protein/kg edible ",""grain" feed only? 1 = yes, 0 = no","LOW N in Animal Excretion (kg-N/animal/yr)","HIGH N in Animal Excretion (kg-N/animal/yr)","LOW Ammonia Emission (kg-N/animal/yr)","HIGH Ammonia Emission (kg-N/animal/yr)")</v>
+      </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B28" s="6"/>
@@ -4950,6 +4976,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d795cf93-200f-4322-ae4e-3af3c2bc7b07">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bec3e06c-9dd4-4aa2-90c9-9a788c41bf59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010050CB5C7BD841A746A008EF8990FEF8A1" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bcac96711073587df0b68b080c708180">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d795cf93-200f-4322-ae4e-3af3c2bc7b07" xmlns:ns3="bec3e06c-9dd4-4aa2-90c9-9a788c41bf59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="98209c71c39a5a5ad103d397a60c957b" ns2:_="" ns3:_="">
     <xsd:import namespace="d795cf93-200f-4322-ae4e-3af3c2bc7b07"/>
@@ -5192,34 +5238,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d795cf93-200f-4322-ae4e-3af3c2bc7b07">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bec3e06c-9dd4-4aa2-90c9-9a788c41bf59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8CD0A9F-452A-4F39-BBF5-3937554EF4A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DFF32F-86D3-4C4C-BD05-44A1DD3358EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="d795cf93-200f-4322-ae4e-3af3c2bc7b07"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="bec3e06c-9dd4-4aa2-90c9-9a788c41bf59"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD6BFFB-E85E-4315-B524-FEE5FF4EEFD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CD6BFFB-E85E-4315-B524-FEE5FF4EEFD2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DFF32F-86D3-4C4C-BD05-44A1DD3358EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8CD0A9F-452A-4F39-BBF5-3937554EF4A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d795cf93-200f-4322-ae4e-3af3c2bc7b07"/>
+    <ds:schemaRef ds:uri="bec3e06c-9dd4-4aa2-90c9-9a788c41bf59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>